--- a/xlsx/packagedataCN20260412-4 industrial40-50.xlsx
+++ b/xlsx/packagedataCN20260412-4 industrial40-50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E967D0D2-ECE7-422C-A7CF-69F0E327377A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBDACCE-5C0D-4295-BBCA-2F9EB62EECE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,50 +34,6 @@
     <t>pkg02</t>
   </si>
   <si>
-    <t>宽度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否堆叠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>包装名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>包装方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>托盘可叉方向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否包箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否转向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,7 +60,51 @@
     <t>pkg04</t>
   </si>
   <si>
-    <t>堆叠层数</t>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Length</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Width</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Height</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quantity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Packing Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forklift Direction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need Boxing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boxing Quantity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rotatable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stackable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -477,42 +477,42 @@
     <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L1" t="s">
         <v>20</v>
@@ -538,21 +538,21 @@
         <v>200</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -576,27 +576,27 @@
         <v>300</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>140</v>
@@ -614,27 +614,27 @@
         <v>600</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>125</v>
@@ -652,27 +652,27 @@
         <v>500</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>140</v>
@@ -690,27 +690,27 @@
         <v>500</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>220</v>
@@ -728,22 +728,22 @@
         <v>500</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
